--- a/Complete Extraction Results.xlsx
+++ b/Complete Extraction Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasif\Documents\Qatar-Environment-and-Energy-Research-Institute-Internship-Work-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15301E46-FD93-4D39-8863-8F7C384CE3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1304A5-8A14-47E6-B8A3-B214B9D9D8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D029F850-DD1B-4CC2-9730-F8119DD79F26}"/>
   </bookViews>
